--- a/BRK.xlsx
+++ b/BRK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E16EB25-A466-41DF-895C-DA766D7B65D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B9A62B-8DB3-41B2-9824-D9447324D047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49030" yWindow="2150" windowWidth="24340" windowHeight="15680" xr2:uid="{5F5DF802-5A85-4E14-9A3B-0D559800B44B}"/>
+    <workbookView xWindow="14080" yWindow="3790" windowWidth="24170" windowHeight="12950" activeTab="1" xr2:uid="{5F5DF802-5A85-4E14-9A3B-0D559800B44B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>tc={B2C25246-0FF8-4797-965E-9B1BAA943271}</author>
   </authors>
   <commentList>
-    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{8FC0D6CF-269C-44FD-BDC8-40A0B27C38D4}">
+    <comment ref="Q38" authorId="0" shapeId="0" xr:uid="{8FC0D6CF-269C-44FD-BDC8-40A0B27C38D4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -54,7 +54,7 @@
     PCC, Lubrizol, IMC, Marmon</t>
       </text>
     </comment>
-    <comment ref="K6" authorId="1" shapeId="0" xr:uid="{0038C80A-8825-4E95-9B72-6DDF6122769A}">
+    <comment ref="Q39" authorId="1" shapeId="0" xr:uid="{0038C80A-8825-4E95-9B72-6DDF6122769A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     Clayton Homes, Shaw (flooring), insulation, roofing</t>
       </text>
     </comment>
-    <comment ref="K7" authorId="2" shapeId="0" xr:uid="{12BE89E6-0277-4612-9839-C5F9ED9E035B}">
+    <comment ref="Q40" authorId="2" shapeId="0" xr:uid="{12BE89E6-0277-4612-9839-C5F9ED9E035B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -70,7 +70,7 @@
     Forest River, Fruit of the Loom, Duracell</t>
       </text>
     </comment>
-    <comment ref="K8" authorId="3" shapeId="0" xr:uid="{F7DB9224-ABE9-4DE9-B29F-C65C33758B2F}">
+    <comment ref="Q41" authorId="3" shapeId="0" xr:uid="{F7DB9224-ABE9-4DE9-B29F-C65C33758B2F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -78,7 +78,7 @@
     NetJets, FlightSafety, TTI, Dairy Queen</t>
       </text>
     </comment>
-    <comment ref="K9" authorId="4" shapeId="0" xr:uid="{B2C25246-0FF8-4797-965E-9B1BAA943271}">
+    <comment ref="Q42" authorId="4" shapeId="0" xr:uid="{B2C25246-0FF8-4797-965E-9B1BAA943271}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
   <si>
     <t>Shares</t>
   </si>
@@ -177,9 +177,6 @@
     <t>Railroad revenue</t>
   </si>
   <si>
-    <t>Energy Operating</t>
-  </si>
-  <si>
     <t>Industrial Products</t>
   </si>
   <si>
@@ -256,6 +253,93 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Energy &amp; Utilities</t>
+  </si>
+  <si>
+    <t>BNSF Revenue</t>
+  </si>
+  <si>
+    <t>BHE Revenue</t>
+  </si>
+  <si>
+    <t>Manufacturing Revenue</t>
+  </si>
+  <si>
+    <t>Service &amp; Retailing Revenue</t>
+  </si>
+  <si>
+    <t>Pilot Revenue</t>
+  </si>
+  <si>
+    <t>McLane Revenue</t>
+  </si>
+  <si>
+    <t>Insurance, Corporate &amp; Other</t>
+  </si>
+  <si>
+    <t>Electricity &amp; Natural Gas</t>
+  </si>
+  <si>
+    <t>Retail &amp; Wholesale</t>
+  </si>
+  <si>
+    <t>Auto sales</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage Distribution</t>
+  </si>
+  <si>
+    <t>Grocery &amp; Convenience Store</t>
+  </si>
+  <si>
+    <t>Industrial &amp; Commercial Products</t>
+  </si>
+  <si>
+    <t>BH Primary Premiums</t>
+  </si>
+  <si>
+    <t>BHRG Premiums</t>
+  </si>
+  <si>
+    <t>Total Underwriting</t>
+  </si>
+  <si>
+    <t>Investment Income</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Losses</t>
+  </si>
+  <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>Benefits</t>
+  </si>
+  <si>
+    <t>GEICO Premiums</t>
+  </si>
+  <si>
+    <t>Q424</t>
+  </si>
+  <si>
+    <t>Q324</t>
+  </si>
+  <si>
+    <t>Q224</t>
+  </si>
+  <si>
+    <t>Q124</t>
   </si>
 </sst>
 </file>
@@ -637,19 +721,19 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K5" dT="2025-03-12T19:38:50.81" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{8FC0D6CF-269C-44FD-BDC8-40A0B27C38D4}">
+  <threadedComment ref="Q38" dT="2025-03-12T19:38:50.81" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{8FC0D6CF-269C-44FD-BDC8-40A0B27C38D4}">
     <text>PCC, Lubrizol, IMC, Marmon</text>
   </threadedComment>
-  <threadedComment ref="K6" dT="2025-03-12T19:39:24.56" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{0038C80A-8825-4E95-9B72-6DDF6122769A}">
+  <threadedComment ref="Q39" dT="2025-03-12T19:39:24.56" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{0038C80A-8825-4E95-9B72-6DDF6122769A}">
     <text>Clayton Homes, Shaw (flooring), insulation, roofing</text>
   </threadedComment>
-  <threadedComment ref="K7" dT="2025-03-12T19:40:02.80" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{12BE89E6-0277-4612-9839-C5F9ED9E035B}">
+  <threadedComment ref="Q40" dT="2025-03-12T19:40:02.80" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{12BE89E6-0277-4612-9839-C5F9ED9E035B}">
     <text>Forest River, Fruit of the Loom, Duracell</text>
   </threadedComment>
-  <threadedComment ref="K8" dT="2025-03-12T19:40:48.83" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{F7DB9224-ABE9-4DE9-B29F-C65C33758B2F}">
+  <threadedComment ref="Q41" dT="2025-03-12T19:40:48.83" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{F7DB9224-ABE9-4DE9-B29F-C65C33758B2F}">
     <text>NetJets, FlightSafety, TTI, Dairy Queen</text>
   </threadedComment>
-  <threadedComment ref="K9" dT="2025-03-12T19:42:27.11" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{B2C25246-0FF8-4797-965E-9B1BAA943271}">
+  <threadedComment ref="Q42" dT="2025-03-12T19:42:27.11" personId="{36DEFB89-B1BB-4F52-8F74-CB8110791D66}" id="{B2C25246-0FF8-4797-965E-9B1BAA943271}">
     <text>Berkshire Hathaway Automotive (69%) of revenue, a dealership, Nebraska Furniture Mart, Borsheim’s, See’s</text>
   </threadedComment>
 </ThreadedComments>
@@ -700,7 +784,7 @@
         <v>1.438223426</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -724,7 +808,7 @@
         <v>652421</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -735,7 +819,7 @@
         <v>338454</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -762,762 +846,2215 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727F065D-B1E2-4A1D-AA03-3C34E2EC4704}">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1796875" customWidth="1"/>
-    <col min="3" max="6" width="9.54296875" style="3" customWidth="1"/>
-    <col min="7" max="11" width="9.54296875" customWidth="1"/>
+    <col min="3" max="12" width="9.54296875" style="3" customWidth="1"/>
+    <col min="13" max="17" width="9.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I2">
+      <c r="L2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2">
         <v>2022</v>
       </c>
-      <c r="J2">
+      <c r="P2">
         <v>2023</v>
       </c>
-      <c r="K2">
+      <c r="Q2">
         <v>2024</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <f>+Q2+1</f>
+        <v>2025</v>
+      </c>
+      <c r="S2">
+        <f>+R2+1</f>
+        <v>2026</v>
+      </c>
+      <c r="T2">
+        <f>+S2+1</f>
+        <v>2027</v>
+      </c>
+      <c r="U2">
+        <f>+T2+1</f>
+        <v>2028</v>
+      </c>
+      <c r="V2">
+        <f>+U2+1</f>
+        <v>2029</v>
+      </c>
+      <c r="W2">
+        <f>+V2+1</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="6">
+        <v>10234</v>
+      </c>
+      <c r="D3" s="6">
+        <v>10469</v>
+      </c>
+      <c r="E3" s="6">
+        <v>10699</v>
+      </c>
+      <c r="F3" s="6">
+        <f>42252-E3-D3-C3</f>
+        <v>10850</v>
+      </c>
+      <c r="G3" s="6">
+        <v>10752</v>
+      </c>
+      <c r="H3" s="6">
+        <v>11064</v>
+      </c>
+      <c r="I3" s="6">
+        <v>11264</v>
+      </c>
+      <c r="J3" s="6">
+        <f>44481-I3-H3-G3</f>
+        <v>11401</v>
+      </c>
+      <c r="K3" s="6">
+        <v>11186</v>
+      </c>
+      <c r="L3" s="6">
+        <v>11291</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4541</v>
+      </c>
+      <c r="D4" s="6">
+        <v>4656</v>
+      </c>
+      <c r="E4" s="6">
+        <v>4685</v>
+      </c>
+      <c r="F4" s="6">
+        <f>18733-E4-D4-C4</f>
+        <v>4851</v>
+      </c>
+      <c r="G4" s="6">
+        <v>4577</v>
+      </c>
+      <c r="H4" s="6">
+        <v>4677</v>
+      </c>
+      <c r="I4" s="6">
+        <v>4711</v>
+      </c>
+      <c r="J4" s="6">
+        <f>18713-I4-H4-G4</f>
+        <v>4748</v>
+      </c>
+      <c r="K4" s="6">
+        <v>4591</v>
+      </c>
+      <c r="L4" s="6">
+        <v>4673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="6">
+        <v>6699</v>
+      </c>
+      <c r="D5" s="6">
+        <v>6828</v>
+      </c>
+      <c r="E5" s="6">
+        <v>6671</v>
+      </c>
+      <c r="F5" s="6">
+        <f>27272-E5-D5-C5</f>
+        <v>7074</v>
+      </c>
+      <c r="G5" s="6">
+        <v>6475</v>
+      </c>
+      <c r="H5" s="6">
+        <v>6454</v>
+      </c>
+      <c r="I5" s="6">
+        <v>6470</v>
+      </c>
+      <c r="J5" s="6">
+        <f>25708-I5-H5-G5</f>
+        <v>6309</v>
+      </c>
+      <c r="K5" s="6">
+        <v>6228</v>
+      </c>
+      <c r="L5" s="6">
+        <v>6511</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="6">
+        <f>+C5+C4+C3</f>
+        <v>21474</v>
+      </c>
+      <c r="D6" s="6">
+        <f>+D5+D4+D3</f>
+        <v>21953</v>
+      </c>
+      <c r="E6" s="6">
+        <f>+E5+E4+E3</f>
+        <v>22055</v>
+      </c>
+      <c r="F6" s="6">
+        <f>+F5+F4+F3</f>
+        <v>22775</v>
+      </c>
+      <c r="G6" s="6">
+        <f>+G5+G4+G3</f>
+        <v>21804</v>
+      </c>
+      <c r="H6" s="6">
+        <f>+H5+H4+H3</f>
+        <v>22195</v>
+      </c>
+      <c r="I6" s="6">
+        <f>+I5+I4+I3</f>
+        <v>22445</v>
+      </c>
+      <c r="J6" s="6">
+        <f>+J5+J4+J3</f>
+        <v>22458</v>
+      </c>
+      <c r="K6" s="6">
+        <f>+K5+K4+K3</f>
+        <v>22005</v>
+      </c>
+      <c r="L6" s="6">
+        <f>+L5+L4+L3</f>
+        <v>22475</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="6">
+        <v>3164</v>
+      </c>
+      <c r="D7" s="6">
+        <v>4077</v>
+      </c>
+      <c r="E7" s="6">
+        <v>4609</v>
+      </c>
+      <c r="F7" s="6">
+        <f>16812-E7-D7-C7</f>
+        <v>4962</v>
+      </c>
+      <c r="G7" s="6">
+        <v>3571</v>
+      </c>
+      <c r="H7" s="6">
+        <v>4053</v>
+      </c>
+      <c r="I7" s="6">
+        <v>3736</v>
+      </c>
+      <c r="J7" s="6">
+        <f>15310-I7-H7-G7</f>
+        <v>3950</v>
+      </c>
+      <c r="K7" s="6">
+        <v>3307</v>
+      </c>
+      <c r="L7" s="6">
+        <v>3701</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="7">
+        <f>+C7+C6</f>
+        <v>24638</v>
+      </c>
+      <c r="D8" s="7">
+        <f>+D7+D6</f>
+        <v>26030</v>
+      </c>
+      <c r="E8" s="7">
+        <f>+E7+E6</f>
+        <v>26664</v>
+      </c>
+      <c r="F8" s="7">
+        <f>+F7+F6</f>
+        <v>27737</v>
+      </c>
+      <c r="G8" s="7">
+        <f>+G7+G6</f>
+        <v>25375</v>
+      </c>
+      <c r="H8" s="7">
+        <f>+H7+H6</f>
+        <v>26248</v>
+      </c>
+      <c r="I8" s="7">
+        <f>+I7+I6</f>
+        <v>26181</v>
+      </c>
+      <c r="J8" s="7">
+        <f>+J7+J6</f>
+        <v>26408</v>
+      </c>
+      <c r="K8" s="7">
+        <f>+K7+K6</f>
+        <v>25312</v>
+      </c>
+      <c r="L8" s="7">
+        <f>+L7+L6</f>
+        <v>26176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="6">
+        <v>13448</v>
+      </c>
+      <c r="D9" s="6">
+        <v>14107</v>
+      </c>
+      <c r="E9" s="6">
+        <v>15163</v>
+      </c>
+      <c r="F9" s="6">
+        <f>56186-E9-D9-C9</f>
+        <v>13468</v>
+      </c>
+      <c r="G9" s="6">
+        <v>14646</v>
+      </c>
+      <c r="H9" s="6">
+        <v>14073</v>
+      </c>
+      <c r="I9" s="6">
+        <v>13735</v>
+      </c>
+      <c r="J9" s="6">
+        <f>57307-I9-H9-G9</f>
+        <v>14853</v>
+      </c>
+      <c r="K9" s="6">
+        <v>14204</v>
+      </c>
+      <c r="L9" s="6">
+        <v>14274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="6">
+        <v>945</v>
+      </c>
+      <c r="D10" s="6">
+        <v>954</v>
+      </c>
+      <c r="E10" s="6">
+        <v>925</v>
+      </c>
+      <c r="F10" s="6">
+        <f>3858-E10-D10-C10</f>
+        <v>1034</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1068</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1132</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1116</v>
+      </c>
+      <c r="J10" s="6">
+        <f>4379-I10-H10-G10</f>
+        <v>1063</v>
+      </c>
+      <c r="K10" s="6">
+        <v>1019</v>
+      </c>
+      <c r="L10" s="6">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="6">
+        <v>3767</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4054</v>
+      </c>
+      <c r="E11" s="6">
+        <v>4948</v>
+      </c>
+      <c r="F11" s="6">
+        <f>16872-E11-D11-C11</f>
+        <v>4103</v>
+      </c>
+      <c r="G11" s="6">
+        <v>4378</v>
+      </c>
+      <c r="H11" s="6">
+        <v>4506</v>
+      </c>
+      <c r="I11" s="6">
+        <v>4451</v>
+      </c>
+      <c r="J11" s="6">
+        <f>17805-I11-H11-G11</f>
+        <v>4470</v>
+      </c>
+      <c r="K11" s="6">
+        <v>4520</v>
+      </c>
+      <c r="L11" s="6">
+        <v>4804</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="6">
+        <f>+C8-C9-C10-C11</f>
+        <v>6478</v>
+      </c>
+      <c r="D12" s="6">
+        <f>+D8-D9-D10-D11</f>
+        <v>6915</v>
+      </c>
+      <c r="E12" s="6">
+        <f>+E8-E9-E10-E11</f>
+        <v>5628</v>
+      </c>
+      <c r="F12" s="6">
+        <f>+F8-F9-F10-F11</f>
+        <v>9132</v>
+      </c>
+      <c r="G12" s="6">
+        <f>+G8-G9-G10-G11</f>
+        <v>5283</v>
+      </c>
+      <c r="H12" s="6">
+        <f>+H8-H9-H10-H11</f>
+        <v>6537</v>
+      </c>
+      <c r="I12" s="6">
+        <f>+I8-I9-I10-I11</f>
+        <v>6879</v>
+      </c>
+      <c r="J12" s="6">
+        <f>+J8-J9-J10-J11</f>
+        <v>6022</v>
+      </c>
+      <c r="K12" s="6">
+        <f>+K8-K9-K10-K11</f>
+        <v>5569</v>
+      </c>
+      <c r="L12" s="6">
+        <f>+L8-L9-L10-L11</f>
+        <v>5865</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="6">
+        <v>5637</v>
+      </c>
+      <c r="D14" s="6">
+        <v>5787</v>
+      </c>
+      <c r="E14" s="6">
+        <v>5920</v>
+      </c>
+      <c r="F14" s="6">
+        <f>23490-E14-D14-C14</f>
+        <v>6146</v>
+      </c>
+      <c r="G14" s="6">
+        <v>5699</v>
+      </c>
+      <c r="H14" s="6">
+        <v>5746</v>
+      </c>
+      <c r="I14" s="6">
+        <v>6013</v>
+      </c>
+      <c r="J14" s="6">
+        <f>23441-I14-H14-G14</f>
+        <v>5983</v>
+      </c>
+      <c r="K14" s="6">
+        <v>5965</v>
+      </c>
+      <c r="L14" s="6">
+        <v>6577</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="6">
+        <v>6265</v>
+      </c>
+      <c r="D15" s="6">
+        <v>6480</v>
+      </c>
+      <c r="E15" s="6">
+        <v>7323</v>
+      </c>
+      <c r="F15" s="6">
+        <f>26300-E15-D15-C15</f>
+        <v>6232</v>
+      </c>
+      <c r="G15" s="6">
+        <v>6344</v>
+      </c>
+      <c r="H15" s="6">
+        <v>6405</v>
+      </c>
+      <c r="I15" s="6">
+        <v>7293</v>
+      </c>
+      <c r="J15" s="6">
+        <f>26282-I15-H15-G15</f>
+        <v>6240</v>
+      </c>
+      <c r="K15" s="6">
+        <v>6658</v>
+      </c>
+      <c r="L15" s="6">
+        <v>6730</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="6">
+        <v>18511</v>
+      </c>
+      <c r="D16" s="6">
+        <v>19807</v>
+      </c>
+      <c r="E16" s="6">
+        <v>19670</v>
+      </c>
+      <c r="F16" s="6">
+        <f>77148-E16-D16-C16</f>
+        <v>19160</v>
+      </c>
+      <c r="G16" s="6">
+        <v>18752</v>
+      </c>
+      <c r="H16" s="6">
+        <v>19940</v>
+      </c>
+      <c r="I16" s="6">
+        <v>20015</v>
+      </c>
+      <c r="J16" s="6">
+        <f>78390-I16-H16-G16</f>
+        <v>19683</v>
+      </c>
+      <c r="K16" s="6">
+        <v>20642</v>
+      </c>
+      <c r="L16" s="6">
+        <v>22520</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="6">
+        <v>9672</v>
+      </c>
+      <c r="D17" s="6">
+        <v>9922</v>
+      </c>
+      <c r="E17" s="6">
+        <v>9828</v>
+      </c>
+      <c r="F17" s="6">
+        <f>39783-E17-D17-C17</f>
+        <v>10361</v>
+      </c>
+      <c r="G17" s="6">
+        <v>10112</v>
+      </c>
+      <c r="H17" s="6">
+        <v>10671</v>
+      </c>
+      <c r="I17" s="6">
+        <v>10568</v>
+      </c>
+      <c r="J17" s="6">
+        <f>42560-I17-H17-G17</f>
+        <v>11209</v>
+      </c>
+      <c r="K17" s="6">
+        <v>10961</v>
+      </c>
+      <c r="L17" s="6">
+        <v>11858</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="6">
+        <v>12494</v>
+      </c>
+      <c r="D18" s="6">
+        <v>12984</v>
+      </c>
+      <c r="E18" s="6">
+        <v>10623</v>
+      </c>
+      <c r="F18" s="6">
+        <f>46856-E18-D18-C18</f>
+        <v>10755</v>
+      </c>
+      <c r="G18" s="6">
+        <v>10422</v>
+      </c>
+      <c r="H18" s="6">
+        <v>10095</v>
+      </c>
+      <c r="I18" s="6">
+        <v>10879</v>
+      </c>
+      <c r="J18" s="6">
+        <f>42166-I18-H18-G18</f>
+        <v>10770</v>
+      </c>
+      <c r="K18" s="6">
+        <v>11229</v>
+      </c>
+      <c r="L18" s="6">
+        <v>14925</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="6">
+        <v>12300</v>
+      </c>
+      <c r="D19" s="6">
+        <v>12271</v>
+      </c>
+      <c r="E19" s="6">
+        <v>12527</v>
+      </c>
+      <c r="F19" s="6">
+        <f>51086-E19-D19-C19</f>
+        <v>13988</v>
+      </c>
+      <c r="G19" s="6">
+        <v>12016</v>
+      </c>
+      <c r="H19" s="6">
+        <v>12399</v>
+      </c>
+      <c r="I19" s="6">
+        <v>12960</v>
+      </c>
+      <c r="J19" s="6">
+        <f>50215-I19-H19-G19</f>
+        <v>12840</v>
+      </c>
+      <c r="K19" s="6">
+        <v>11759</v>
+      </c>
+      <c r="L19" s="6">
+        <v>11888</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="6">
+        <v>24990</v>
+      </c>
+      <c r="D20" s="6">
+        <v>26402</v>
+      </c>
+      <c r="E20" s="6">
+        <v>27104</v>
+      </c>
+      <c r="F20" s="6">
+        <f>106770-E20-D20-C20</f>
+        <v>28274</v>
+      </c>
+      <c r="G20" s="6">
+        <v>26380</v>
+      </c>
+      <c r="H20" s="6">
+        <v>27259</v>
+      </c>
+      <c r="I20" s="6">
+        <v>27244</v>
+      </c>
+      <c r="J20" s="6">
+        <f>108390-I20-H20-G20</f>
+        <v>27507</v>
+      </c>
+      <c r="K20" s="6">
+        <v>26461</v>
+      </c>
+      <c r="L20" s="6">
+        <v>27310</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="7">
+        <f>SUM(C14:C20)</f>
+        <v>89869</v>
+      </c>
+      <c r="D21" s="7">
+        <f>SUM(D14:D20)</f>
+        <v>93653</v>
+      </c>
+      <c r="E21" s="7">
+        <f>SUM(E14:E20)</f>
+        <v>92995</v>
+      </c>
+      <c r="F21" s="7">
+        <f>SUM(F14:F20)</f>
+        <v>94916</v>
+      </c>
+      <c r="G21" s="7">
+        <f>SUM(G14:G20)</f>
+        <v>89725</v>
+      </c>
+      <c r="H21" s="7">
+        <f>SUM(H14:H20)</f>
+        <v>92515</v>
+      </c>
+      <c r="I21" s="7">
+        <f>SUM(I14:I20)</f>
+        <v>94972</v>
+      </c>
+      <c r="J21" s="7">
+        <f>SUM(J14:J20)</f>
+        <v>94232</v>
+      </c>
+      <c r="K21" s="7">
+        <f>SUM(K14:K20)</f>
+        <v>93675</v>
+      </c>
+      <c r="L21" s="7">
+        <f>SUM(L14:L20)</f>
+        <v>101808</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="6">
+        <v>7262</v>
+      </c>
+      <c r="D23" s="6">
+        <v>7514</v>
+      </c>
+      <c r="E23" s="6">
+        <v>7234</v>
+      </c>
+      <c r="F23" s="6">
+        <f>29117-E23-D23-C23</f>
+        <v>7107</v>
+      </c>
+      <c r="G23" s="6">
+        <v>7426</v>
+      </c>
+      <c r="H23" s="6">
+        <v>7747</v>
+      </c>
+      <c r="I23" s="6">
+        <v>7664</v>
+      </c>
+      <c r="J23" s="6">
+        <f>30336-I23-H23-G23</f>
+        <v>7499</v>
+      </c>
+      <c r="K23" s="6">
+        <v>9223</v>
+      </c>
+      <c r="L23" s="6">
+        <v>9820</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="6">
+        <v>4674</v>
+      </c>
+      <c r="D24" s="6">
+        <v>5233</v>
+      </c>
+      <c r="E24" s="6">
+        <v>5176</v>
+      </c>
+      <c r="F24" s="6">
+        <f>19892-E24-D24-C24</f>
+        <v>4809</v>
+      </c>
+      <c r="G24" s="6">
+        <v>4588</v>
+      </c>
+      <c r="H24" s="6">
+        <v>5123</v>
+      </c>
+      <c r="I24" s="6">
+        <v>5106</v>
+      </c>
+      <c r="J24" s="6">
+        <f>19609-I24-H24-G24</f>
+        <v>4792</v>
+      </c>
+      <c r="K24" s="6">
+        <v>4668</v>
+      </c>
+      <c r="L24" s="6">
+        <v>5255</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="6">
+        <v>4193</v>
+      </c>
+      <c r="D25" s="6">
+        <v>4588</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4749</v>
+      </c>
+      <c r="F25" s="6">
+        <f>18204-E25-D25-C25</f>
+        <v>4674</v>
+      </c>
+      <c r="G25" s="6">
+        <v>4260</v>
+      </c>
+      <c r="H25" s="6">
+        <v>4361</v>
+      </c>
+      <c r="I25" s="6">
+        <v>4598</v>
+      </c>
+      <c r="J25" s="6">
+        <f>17919-I25-H25-G25</f>
+        <v>4700</v>
+      </c>
+      <c r="K25" s="6">
+        <v>4051</v>
+      </c>
+      <c r="L25" s="6">
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="6">
+        <v>7602</v>
+      </c>
+      <c r="D26" s="6">
+        <v>7500</v>
+      </c>
+      <c r="E26" s="6">
+        <v>7882</v>
+      </c>
+      <c r="F26" s="6">
+        <f>31841-E26-D26-C26</f>
+        <v>8857</v>
+      </c>
+      <c r="G26" s="6">
+        <v>7442</v>
+      </c>
+      <c r="H26" s="6">
+        <v>7516</v>
+      </c>
+      <c r="I26" s="6">
+        <v>7884</v>
+      </c>
+      <c r="J26" s="6">
+        <f>30697-I26-H26-G26</f>
+        <v>7855</v>
+      </c>
+      <c r="K26" s="6">
+        <v>6790</v>
+      </c>
+      <c r="L26" s="6">
+        <v>6704</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="6">
+        <v>4436</v>
+      </c>
+      <c r="D27" s="6">
+        <v>4478</v>
+      </c>
+      <c r="E27" s="6">
+        <v>4372</v>
+      </c>
+      <c r="F27" s="6">
+        <f>18068-E27-D27-C27</f>
+        <v>4782</v>
+      </c>
+      <c r="G27" s="6">
+        <v>4373</v>
+      </c>
+      <c r="H27" s="6">
+        <v>4663</v>
+      </c>
+      <c r="I27" s="6">
+        <v>4836</v>
+      </c>
+      <c r="J27" s="6">
+        <f>18585-I27-H27-G27</f>
+        <v>4713</v>
+      </c>
+      <c r="K27" s="6">
+        <v>4698</v>
+      </c>
+      <c r="L27" s="6">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2552</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2714</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2722</v>
+      </c>
+      <c r="F28" s="6">
+        <f>10802-E28-D28-C28</f>
+        <v>2814</v>
+      </c>
+      <c r="G28" s="6">
+        <v>2701</v>
+      </c>
+      <c r="H28" s="6">
+        <v>2991</v>
+      </c>
+      <c r="I28" s="6">
+        <v>2836</v>
+      </c>
+      <c r="J28" s="6">
+        <f>11283-I28-H28-G28</f>
+        <v>2755</v>
+      </c>
+      <c r="K28" s="6">
+        <v>2591</v>
+      </c>
+      <c r="L28" s="6">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="6">
+        <v>16980</v>
+      </c>
+      <c r="D29" s="6">
+        <v>17461</v>
+      </c>
+      <c r="E29" s="6">
+        <v>14929</v>
+      </c>
+      <c r="F29" s="6">
+        <f>64858-E29-D29-C29</f>
+        <v>15488</v>
+      </c>
+      <c r="G29" s="6">
+        <v>14599</v>
+      </c>
+      <c r="H29" s="6">
+        <v>14733</v>
+      </c>
+      <c r="I29" s="6">
+        <v>15384</v>
+      </c>
+      <c r="J29" s="6">
+        <f>60598-I29-H29-G29</f>
+        <v>15882</v>
+      </c>
+      <c r="K29" s="6">
+        <v>16262</v>
+      </c>
+      <c r="L29" s="6">
+        <v>20262</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>8463</v>
+      </c>
+      <c r="D30" s="6">
+        <v>9054</v>
+      </c>
+      <c r="E30" s="6">
+        <v>9150</v>
+      </c>
+      <c r="F30" s="6">
+        <f>35941-E30-D30-C30</f>
+        <v>9274</v>
+      </c>
+      <c r="G30" s="6">
+        <v>8622</v>
+      </c>
+      <c r="H30" s="6">
+        <v>9327</v>
+      </c>
+      <c r="I30" s="6">
+        <v>9523</v>
+      </c>
+      <c r="J30" s="6">
+        <f>36879-I30-H30-G30</f>
+        <v>9407</v>
+      </c>
+      <c r="K30" s="6">
+        <v>9182</v>
+      </c>
+      <c r="L30" s="6">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="6">
+        <v>5129</v>
+      </c>
+      <c r="D31" s="6">
+        <v>4977</v>
+      </c>
+      <c r="E31" s="6">
+        <v>5834</v>
+      </c>
+      <c r="F31" s="6">
+        <f>20991-E31-D31-C31</f>
+        <v>5051</v>
+      </c>
+      <c r="G31" s="6">
+        <v>5346</v>
+      </c>
+      <c r="H31" s="6">
+        <v>5025</v>
+      </c>
+      <c r="I31" s="6">
+        <v>5916</v>
+      </c>
+      <c r="J31" s="6">
+        <f>21338-I31-H31-G31</f>
+        <v>5051</v>
+      </c>
+      <c r="K31" s="6">
+        <v>5672</v>
+      </c>
+      <c r="L31" s="6">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="6">
+        <v>28578</v>
+      </c>
+      <c r="D32" s="6">
+        <v>30134</v>
+      </c>
+      <c r="E32" s="6">
+        <v>30947</v>
+      </c>
+      <c r="F32" s="6">
+        <f>121719-E32-D32-C32</f>
+        <v>32060</v>
+      </c>
+      <c r="G32" s="6">
+        <v>30368</v>
+      </c>
+      <c r="H32" s="6">
+        <v>31109</v>
+      </c>
+      <c r="I32" s="6">
+        <v>31225</v>
+      </c>
+      <c r="J32" s="6">
+        <f>124200-I32-H32-G32</f>
+        <v>31498</v>
+      </c>
+      <c r="K32" s="6">
+        <v>30538</v>
+      </c>
+      <c r="L32" s="6">
+        <v>31693</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="7">
+        <f>SUM(C23:C32)</f>
+        <v>89869</v>
+      </c>
+      <c r="D33" s="7">
+        <f>SUM(D23:D32)</f>
+        <v>93653</v>
+      </c>
+      <c r="E33" s="7">
+        <f>SUM(E23:E32)</f>
+        <v>92995</v>
+      </c>
+      <c r="F33" s="7">
+        <f>SUM(F23:F32)</f>
+        <v>94916</v>
+      </c>
+      <c r="G33" s="7">
+        <f>SUM(G23:G32)</f>
+        <v>89725</v>
+      </c>
+      <c r="H33" s="7">
+        <f>SUM(H23:H32)</f>
+        <v>92595</v>
+      </c>
+      <c r="I33" s="7">
+        <f>SUM(I23:I32)</f>
+        <v>94972</v>
+      </c>
+      <c r="J33" s="7">
+        <f>SUM(J23:J32)</f>
+        <v>94152</v>
+      </c>
+      <c r="K33" s="7">
+        <f>SUM(K23:K32)</f>
+        <v>93675</v>
+      </c>
+      <c r="L33" s="7">
+        <f>SUM(L23:L32)</f>
+        <v>101808</v>
+      </c>
+    </row>
+    <row r="36" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="I3" s="1">
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6">
+        <v>5718</v>
+      </c>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6">
+        <v>6577</v>
+      </c>
+      <c r="O36" s="1">
         <v>25203</v>
       </c>
-      <c r="J3" s="1">
+      <c r="P36" s="1">
         <v>23474</v>
       </c>
-      <c r="K3" s="1">
+      <c r="Q36" s="1">
         <v>23355</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+    <row r="37" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6">
+        <v>5118</v>
+      </c>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6">
+        <v>5408</v>
+      </c>
+      <c r="O37" s="1">
+        <v>21069</v>
+      </c>
+      <c r="P37" s="1">
+        <v>21280</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>21566</v>
+      </c>
+    </row>
+    <row r="38" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="I4" s="1">
-        <v>21069</v>
-      </c>
-      <c r="J4" s="1">
-        <v>21280</v>
-      </c>
-      <c r="K4" s="1">
-        <v>21566</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6">
+        <v>9820</v>
+      </c>
+      <c r="O38" s="1">
+        <v>30824</v>
+      </c>
+      <c r="P38" s="1">
+        <v>34884</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>35833</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="I5" s="1">
-        <v>30824</v>
-      </c>
-      <c r="J5" s="1">
-        <v>34884</v>
-      </c>
-      <c r="K5" s="1">
-        <v>35833</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6">
+        <v>5255</v>
+      </c>
+      <c r="O39" s="1">
+        <v>28896</v>
+      </c>
+      <c r="P39" s="1">
+        <v>25965</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>26525</v>
+      </c>
+    </row>
+    <row r="40" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="I6" s="1">
-        <v>28896</v>
-      </c>
-      <c r="J6" s="1">
-        <v>25965</v>
-      </c>
-      <c r="K6" s="1">
-        <v>26525</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6">
+        <v>4333</v>
+      </c>
+      <c r="O40" s="1">
+        <v>16061</v>
+      </c>
+      <c r="P40" s="1">
+        <v>14556</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>14873</v>
+      </c>
+    </row>
+    <row r="41" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="I7" s="1">
-        <v>16061</v>
-      </c>
-      <c r="J7" s="1">
-        <v>14556</v>
-      </c>
-      <c r="K7" s="1">
-        <v>14873</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6">
+        <v>1315</v>
+      </c>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="O41" s="1">
+        <v>19006</v>
+      </c>
+      <c r="P41" s="1">
+        <v>20588</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>20697</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="I8" s="1">
-        <v>19006</v>
-      </c>
-      <c r="J8" s="1">
-        <v>20588</v>
-      </c>
-      <c r="K8" s="1">
-        <v>20697</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6">
+        <v>11858</v>
+      </c>
+      <c r="O42" s="1">
+        <v>19297</v>
+      </c>
+      <c r="P42" s="1">
+        <v>19408</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>19177</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6">
+        <v>14925</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <v>51739</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>46891</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="I9" s="1">
-        <v>19297</v>
-      </c>
-      <c r="J9" s="1">
-        <v>19408</v>
-      </c>
-      <c r="K9" s="1">
-        <v>19177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6">
+        <v>11888</v>
+      </c>
+      <c r="O44" s="1">
+        <v>53209</v>
+      </c>
+      <c r="P44" s="1">
+        <v>52607</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>51907</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B45" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="I10" s="1">
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7">
+        <f>SUM(L36:L44)</f>
+        <v>70064</v>
+      </c>
+      <c r="O45" s="5">
+        <f>SUM(O36:O44)</f>
+        <v>213565</v>
+      </c>
+      <c r="P45" s="5">
+        <f>SUM(P36:P44)</f>
+        <v>264501</v>
+      </c>
+      <c r="Q45" s="5">
+        <f>SUM(Q36:Q44)</f>
+        <v>260824</v>
+      </c>
+      <c r="R45" s="5">
+        <f>SUM(R36:R44)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="1">
-        <v>51739</v>
-      </c>
-      <c r="K10" s="1">
-        <v>46891</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="I11" s="1">
-        <v>53209</v>
-      </c>
-      <c r="J11" s="1">
-        <v>52607</v>
-      </c>
-      <c r="K11" s="1">
-        <v>51907</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" s="5">
-        <f>SUM(I3:I11)</f>
-        <v>213565</v>
-      </c>
-      <c r="J12" s="5">
-        <f>SUM(J3:J11)</f>
-        <v>264501</v>
-      </c>
-      <c r="K12" s="5">
-        <f>SUM(K3:K11)</f>
-        <v>260824</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+      <c r="S45" s="5">
+        <f>SUM(S36:S44)</f>
+        <v>0</v>
+      </c>
+      <c r="T45" s="5">
+        <f>SUM(T36:T44)</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="5">
+        <f>SUM(U36:U44)</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="5">
+        <f>SUM(V36:V44)</f>
+        <v>0</v>
+      </c>
+      <c r="W45" s="5">
+        <f>SUM(W36:W44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1">
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1">
         <v>-1880</v>
       </c>
-      <c r="J14" s="1">
+      <c r="P47" s="1">
         <v>3635</v>
       </c>
-      <c r="K14" s="1">
+      <c r="Q47" s="1">
         <v>7813</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1">
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1">
         <v>393</v>
       </c>
-      <c r="J15" s="1">
+      <c r="P48" s="1">
         <v>1374</v>
       </c>
-      <c r="K15" s="1">
+      <c r="Q48" s="1">
         <v>855</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1">
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1">
         <v>1465</v>
       </c>
-      <c r="J16" s="1">
+      <c r="P49" s="1">
         <v>1904</v>
       </c>
-      <c r="K16" s="1">
+      <c r="Q49" s="1">
         <v>2737</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1">
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1">
         <v>8</v>
       </c>
-      <c r="J17" s="1">
+      <c r="P50" s="1">
         <v>1485</v>
       </c>
-      <c r="K17" s="1">
+      <c r="Q50" s="1">
         <v>2385</v>
       </c>
     </row>
-    <row r="18" spans="2:11" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B18" s="5" t="s">
+    <row r="51" spans="2:17" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B51" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="I18" s="5">
-        <f>+I14+I15+I16-I17</f>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="O51" s="5">
+        <f>+O47+O48+O49-O50</f>
         <v>-30</v>
       </c>
-      <c r="J18" s="5">
-        <f>+J14+J15+J16-J17</f>
+      <c r="P51" s="5">
+        <f>+P47+P48+P49-P50</f>
         <v>5428</v>
       </c>
-      <c r="K18" s="5">
-        <f>+K14+K15+K16-K17</f>
+      <c r="Q51" s="5">
+        <f>+Q47+Q48+Q49-Q50</f>
         <v>9020</v>
       </c>
     </row>
-    <row r="19" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+    <row r="52" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="I19" s="1">
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="O52" s="1">
         <v>6484</v>
       </c>
-      <c r="J19" s="1">
+      <c r="P52" s="1">
         <v>9567</v>
       </c>
-      <c r="K19" s="1">
+      <c r="Q52" s="1">
         <v>13670</v>
       </c>
     </row>
-    <row r="20" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
+    <row r="53" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="I20" s="1">
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="O53" s="1">
         <v>5946</v>
       </c>
-      <c r="J20" s="1">
+      <c r="P53" s="1">
         <v>5087</v>
       </c>
-      <c r="K20" s="1">
+      <c r="Q53" s="1">
         <v>5031</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1">
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1">
         <v>3904</v>
       </c>
-      <c r="J21" s="1">
+      <c r="P54" s="1">
         <v>2331</v>
       </c>
-      <c r="K21" s="1">
+      <c r="Q54" s="1">
         <v>3730</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1">
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1">
         <v>12512</v>
       </c>
-      <c r="J22" s="1">
+      <c r="P55" s="1">
         <v>13362</v>
       </c>
-      <c r="K22" s="1">
+      <c r="Q55" s="1">
         <v>13072</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1">
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1">
         <v>1528</v>
       </c>
-      <c r="J23" s="1">
+      <c r="P56" s="1">
         <v>1750</v>
       </c>
-      <c r="K23" s="1">
+      <c r="Q56" s="1">
         <v>1519</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1">
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1">
         <v>-53612</v>
       </c>
-      <c r="J24" s="1">
+      <c r="P57" s="1">
         <v>58873</v>
       </c>
-      <c r="K24" s="1">
+      <c r="Q57" s="1">
         <v>41558</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1">
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1">
         <v>509</v>
       </c>
-      <c r="J25" s="1">
+      <c r="P58" s="1">
         <v>-175</v>
       </c>
-      <c r="K25" s="1">
+      <c r="Q58" s="1">
         <v>1395</v>
       </c>
     </row>
-    <row r="26" spans="2:11" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B26" s="5" t="s">
+    <row r="59" spans="2:17" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B59" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5">
-        <f>SUM(I18:I25)</f>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5">
+        <f>SUM(O51:O58)</f>
         <v>-22759</v>
       </c>
-      <c r="J26" s="5">
-        <f>SUM(J18:J25)</f>
+      <c r="P59" s="5">
+        <f>SUM(P51:P58)</f>
         <v>96223</v>
       </c>
-      <c r="K26" s="5">
-        <f>SUM(K18:K25)</f>
+      <c r="Q59" s="5">
+        <f>SUM(Q51:Q58)</f>
         <v>88995</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1">
-        <f>+I26-I24</f>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1">
+        <f>+O59-O57</f>
         <v>30853</v>
       </c>
-      <c r="J27" s="1">
-        <f>+J26-J24</f>
+      <c r="P60" s="1">
+        <f>+P59-P57</f>
         <v>37350</v>
       </c>
-      <c r="K27" s="1">
-        <f>+K26-K24</f>
+      <c r="Q60" s="1">
+        <f>+Q59-Q57</f>
         <v>47437</v>
       </c>
     </row>
-    <row r="31" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
+    <row r="64" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6">
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6">
         <f>96193+243605+15084+267923+25323+4293</f>
         <v>652421</v>
       </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="K31" s="1">
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="Q64" s="1">
         <f>44333+286472+15364+271588+31134+3396</f>
         <v>652287</v>
       </c>
     </row>
-    <row r="32" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6">
+    <row r="65" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6">
         <f>30374+179366</f>
         <v>209740</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="K32" s="1">
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="Q65" s="1">
         <f>30071+175030</f>
         <v>205101</v>
       </c>
     </row>
-    <row r="33" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6">
+    <row r="66" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6">
         <v>28722</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="K33" s="1">
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="Q66" s="1">
         <v>27798</v>
       </c>
     </row>
-    <row r="34" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6">
+    <row r="67" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6">
         <f>47473+4323</f>
         <v>51796</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="K34" s="1">
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="Q67" s="1">
         <f>43887+4503</f>
         <v>48390</v>
       </c>
     </row>
-    <row r="35" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="1" t="s">
+    <row r="68" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6">
+        <v>24371</v>
+      </c>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="Q68" s="1">
+        <v>24008</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6">
-        <v>24371</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="K35" s="1">
-        <v>24008</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6">
+        <v>18123</v>
+      </c>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="Q69" s="1">
+        <v>17828</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6">
-        <v>18123</v>
-      </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="K36" s="1">
-        <v>17828</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6">
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6">
         <f>57096+34079+27155</f>
         <v>118330</v>
       </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="K37" s="1">
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="Q70" s="1">
         <f>56860+34638+27020</f>
         <v>118518</v>
       </c>
     </row>
-    <row r="38" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6">
+    <row r="71" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6">
         <v>8474</v>
       </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="K38" s="1">
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="Q71" s="1">
         <v>8797</v>
       </c>
     </row>
-    <row r="39" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
+    <row r="72" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6">
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6">
         <f>25699+21051+5241</f>
         <v>51991</v>
       </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="K39" s="1">
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="Q72" s="1">
         <f>20811+24994+5349</f>
         <v>51154</v>
       </c>
     </row>
-    <row r="40" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6">
-        <f>SUM(D31:D39)</f>
+    <row r="73" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6">
+        <f>SUM(H64:H72)</f>
         <v>1163968</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="K40" s="1">
-        <f>SUM(K31:K39)</f>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="Q73" s="1">
+        <f>SUM(Q64:Q72)</f>
         <v>1153881</v>
       </c>
     </row>
-    <row r="42" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
+    <row r="75" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6">
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6">
         <f>118788+31733+32414+17865+10634+45040+81980</f>
         <v>338454</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="K42" s="1">
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="Q75" s="1">
         <f>115151+32443+17616+10703+12769+79877+44885+30808</f>
         <v>344252</v>
       </c>
     </row>
-    <row r="43" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6">
+    <row r="76" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6">
         <f>36988+18382</f>
         <v>55370</v>
       </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="K43" s="1">
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="Q76" s="1">
         <f>18226+37489</f>
         <v>55715</v>
       </c>
     </row>
-    <row r="44" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="1" t="s">
+    <row r="77" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6">
+        <v>9747</v>
+      </c>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="Q77" s="1">
+        <v>9356</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <v>9747</v>
-      </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="K44" s="1">
-        <v>9356</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6">
+        <v>82991</v>
+      </c>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="Q78" s="1">
+        <v>85870</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6">
-        <v>82991</v>
-      </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="K45" s="1">
-        <v>85870</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6">
+        <v>7130</v>
+      </c>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="Q79" s="1">
+        <v>7033</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6">
-        <v>7130</v>
-      </c>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="K46" s="1">
-        <v>7033</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6">
+        <v>670276</v>
+      </c>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+      <c r="Q80" s="1">
+        <v>651655</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6">
-        <v>670276</v>
-      </c>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="K47" s="1">
-        <v>651655</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="1">
-        <f>SUM(D42:D47)</f>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="1">
+        <f>SUM(H75:H80)</f>
         <v>1163968</v>
       </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="K48" s="1">
-        <f>SUM(K42:K47)</f>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="Q81" s="1">
+        <f>SUM(Q75:Q80)</f>
         <v>1153881</v>
       </c>
     </row>
